--- a/education_surveys/021_environmental_lifestyle_choices_survey--education_surveys.xlsx
+++ b/education_surveys/021_environmental_lifestyle_choices_survey--education_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -849,8 +849,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="29" customWidth="1" min="2" max="2"/>
-    <col width="29" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -878,12 +878,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'car'}</t>
+          <t>car</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Car'}</t>
+          <t>Car</t>
         </is>
       </c>
     </row>
@@ -895,12 +895,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'bike'}</t>
+          <t>bike</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Bike'}</t>
+          <t>Bike</t>
         </is>
       </c>
     </row>
@@ -912,12 +912,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'walking'}</t>
+          <t>walking</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Walking'}</t>
+          <t>Walking</t>
         </is>
       </c>
     </row>
@@ -929,12 +929,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -946,12 +946,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'gas'}</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Gas'}</t>
+          <t>Gas</t>
         </is>
       </c>
     </row>
@@ -963,12 +963,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'electricity'}</t>
+          <t>electricity</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Electricity'}</t>
+          <t>Electricity</t>
         </is>
       </c>
     </row>
@@ -980,12 +980,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'water'}</t>
+          <t>water</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Water'}</t>
+          <t>Water</t>
         </is>
       </c>
     </row>
@@ -997,12 +997,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'vegetarian'}</t>
+          <t>vegetarian</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Vegetarian'}</t>
+          <t>Vegetarian</t>
         </is>
       </c>
     </row>
@@ -1014,12 +1014,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'vegan'}</t>
+          <t>vegan</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Vegan'}</t>
+          <t>Vegan</t>
         </is>
       </c>
     </row>
@@ -1031,12 +1031,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'omnivore'}</t>
+          <t>omnivore</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Omnivore'}</t>
+          <t>Omnivore</t>
         </is>
       </c>
     </row>
@@ -1048,12 +1048,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1065,12 +1065,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'gas'}</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'Gas'}</t>
+          <t>Gas</t>
         </is>
       </c>
     </row>
@@ -1082,12 +1082,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'electricity'}</t>
+          <t>electricity</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'Electricity'}</t>
+          <t>Electricity</t>
         </is>
       </c>
     </row>
@@ -1099,12 +1099,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'solar'}</t>
+          <t>solar</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'Solar'}</t>
+          <t>Solar</t>
         </is>
       </c>
     </row>
@@ -1116,12 +1116,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'low'}</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'Low'}</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -1133,12 +1133,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_'medium'}</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': 'Medium'}</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -1150,12 +1150,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_'high'}</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': 'High'}</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -1167,12 +1167,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'label':_'high_school'}</t>
+          <t>high_school</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'label': 'High School'}</t>
+          <t>High School</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'label':_'college'}</t>
+          <t>college</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'label': 'College'}</t>
+          <t>College</t>
         </is>
       </c>
     </row>
@@ -1201,12 +1201,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'label':_'post_graduate'}</t>
+          <t>post_graduate</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'label': 'Post Graduate'}</t>
+          <t>Post Graduate</t>
         </is>
       </c>
     </row>
@@ -1218,12 +1218,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'label':_'local_events'}</t>
+          <t>local_events</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'label': 'Local events'}</t>
+          <t>Local events</t>
         </is>
       </c>
     </row>
@@ -1235,12 +1235,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'label':_'online_groups'}</t>
+          <t>online_groups</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'label': 'Online groups'}</t>
+          <t>Online groups</t>
         </is>
       </c>
     </row>
@@ -1252,12 +1252,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'label':_'both'}</t>
+          <t>both</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'label': 'Both'}</t>
+          <t>Both</t>
         </is>
       </c>
     </row>
@@ -1269,12 +1269,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'label':_'environment'}</t>
+          <t>environment</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'label': 'Environment'}</t>
+          <t>Environment</t>
         </is>
       </c>
     </row>
@@ -1286,12 +1286,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'label':_'money'}</t>
+          <t>money</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'label': 'Money'}</t>
+          <t>Money</t>
         </is>
       </c>
     </row>
@@ -1303,12 +1303,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'label':_'health'}</t>
+          <t>health</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'label': 'Health'}</t>
+          <t>Health</t>
         </is>
       </c>
     </row>
@@ -1320,12 +1320,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'label':_'very_important'}</t>
+          <t>very_important</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'label': 'Very important'}</t>
+          <t>Very important</t>
         </is>
       </c>
     </row>
@@ -1337,12 +1337,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'label':_'important'}</t>
+          <t>important</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'label': 'Important'}</t>
+          <t>Important</t>
         </is>
       </c>
     </row>
@@ -1354,12 +1354,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'label':_'not_important'}</t>
+          <t>not_important</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'label': 'Not important'}</t>
+          <t>Not important</t>
         </is>
       </c>
     </row>
@@ -1371,12 +1371,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'label':_'short'}</t>
+          <t>short</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'label': 'Short'}</t>
+          <t>Short</t>
         </is>
       </c>
     </row>
@@ -1388,12 +1388,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'label':_'long'}</t>
+          <t>long</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'label': 'Long'}</t>
+          <t>Long</t>
         </is>
       </c>
     </row>
@@ -1405,12 +1405,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
